--- a/Python/dz2/work/output/shelter_statistics.xlsx
+++ b/Python/dz2/work/output/shelter_statistics.xlsx
@@ -697,13 +697,13 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G16">
-        <v>77.62</v>
+        <v>78.62</v>
       </c>
       <c r="H16">
         <v>34.16</v>
